--- a/SCIE용/산출물/엑셀/15_g1_g2_g3_g4_retrieval_results.xlsx
+++ b/SCIE용/산출물/엑셀/15_g1_g2_g3_g4_retrieval_results.xlsx
@@ -225,54 +225,62 @@
       </c>
       <c r="H2" s="0" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I2" s="0" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J2" s="0" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I2" s="0" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J2" s="0" t="inlineStr">
+      <c r="K2" s="0" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L2" s="0" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K2" s="0" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L2" s="0" t="inlineStr">
+      <c r="M2" s="0" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N2" s="0" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O2" s="0" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P2" s="0" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="M2" s="0" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="N2" s="0"/>
-      <c r="O2" s="0" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P2" s="0" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="Q2" s="0" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="R2" s="0"/>
+      <c r="R2" s="0" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="S2" s="0" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
     </row>
@@ -342,10 +350,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N3" s="0"/>
+      <c r="N3" s="0" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O3" s="0" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P3" s="0" t="inlineStr">
@@ -360,7 +372,7 @@
       </c>
       <c r="R3" s="0" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S3" s="0" t="inlineStr">
@@ -534,27 +546,27 @@
       </c>
       <c r="N5" s="0" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O5" s="0" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P5" s="0" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q5" s="0" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="R5" s="0" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="O5" s="0" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P5" s="0" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Q5" s="0" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="R5" s="0" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="S5" s="0" t="inlineStr">
@@ -718,10 +730,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N7" s="0"/>
+      <c r="N7" s="0" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="O7" s="0" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>△</t>
         </is>
       </c>
       <c r="P7" s="0" t="inlineStr">
@@ -736,12 +752,12 @@
       </c>
       <c r="R7" s="0" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="S7" s="0" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>O</t>
         </is>
       </c>
     </row>
@@ -813,12 +829,12 @@
       </c>
       <c r="N8" s="0" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O8" s="0" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P8" s="0" t="inlineStr">
@@ -833,7 +849,7 @@
       </c>
       <c r="R8" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S8" s="0" t="inlineStr">
@@ -930,7 +946,7 @@
       </c>
       <c r="R9" s="0" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="S9" s="0" t="inlineStr">
@@ -1007,7 +1023,7 @@
       </c>
       <c r="N10" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O10" s="0" t="inlineStr">
@@ -1027,7 +1043,7 @@
       </c>
       <c r="R10" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S10" s="0" t="inlineStr">
@@ -1074,7 +1090,7 @@
       </c>
       <c r="H11" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I11" s="0" t="inlineStr">
@@ -1084,7 +1100,7 @@
       </c>
       <c r="J11" s="0" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K11" s="0" t="inlineStr">
@@ -1094,7 +1110,7 @@
       </c>
       <c r="L11" s="0" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M11" s="0" t="inlineStr">
@@ -1110,7 +1126,7 @@
       </c>
       <c r="P11" s="0" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Q11" s="0" t="inlineStr">
@@ -1191,10 +1207,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N12" s="0"/>
+      <c r="N12" s="0" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="O12" s="0" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P12" s="0" t="inlineStr">
@@ -1207,10 +1227,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R12" s="0"/>
+      <c r="R12" s="0" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="S12" s="0" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1306,7 @@
       </c>
       <c r="N13" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O13" s="0" t="inlineStr">
@@ -1302,7 +1326,7 @@
       </c>
       <c r="R13" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="S13" s="0" t="inlineStr">
@@ -1399,7 +1423,7 @@
       </c>
       <c r="R14" s="0" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="S14" s="0" t="inlineStr">
@@ -1571,10 +1595,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N16" s="0"/>
+      <c r="N16" s="0" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O16" s="0" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P16" s="0" t="inlineStr">
@@ -1587,10 +1615,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R16" s="0"/>
+      <c r="R16" s="0" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="S16" s="0" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
     </row>
@@ -1632,12 +1664,12 @@
       </c>
       <c r="H17" s="0" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I17" s="0" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>△</t>
         </is>
       </c>
       <c r="J17" s="0" t="inlineStr">
@@ -1759,7 +1791,7 @@
       </c>
       <c r="N18" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O18" s="0" t="inlineStr">
@@ -1779,7 +1811,7 @@
       </c>
       <c r="R18" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S18" s="0" t="inlineStr">
@@ -1951,10 +1983,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N20" s="0"/>
+      <c r="N20" s="0" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="O20" s="0" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>△</t>
         </is>
       </c>
       <c r="P20" s="0" t="inlineStr">
@@ -1969,12 +2005,12 @@
       </c>
       <c r="R20" s="0" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="S20" s="0" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>O</t>
         </is>
       </c>
     </row>
@@ -2016,57 +2052,57 @@
       </c>
       <c r="H21" s="0" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I21" s="0" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J21" s="0" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K21" s="0" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L21" s="0" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M21" s="0" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N21" s="0" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I21" s="0" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J21" s="0" t="inlineStr">
+      <c r="O21" s="0" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P21" s="0" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q21" s="0" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="R21" s="0" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="K21" s="0" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L21" s="0" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M21" s="0" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="N21" s="0" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O21" s="0" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P21" s="0" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Q21" s="0" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="R21" s="0" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="S21" s="0" t="inlineStr">
@@ -2123,7 +2159,7 @@
       </c>
       <c r="J22" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K22" s="0" t="inlineStr">
@@ -2133,7 +2169,7 @@
       </c>
       <c r="L22" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M22" s="0" t="inlineStr">
@@ -2143,19 +2179,19 @@
       </c>
       <c r="N22" s="0" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O22" s="0" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P22" s="0" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="O22" s="0" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P22" s="0" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="Q22" s="0" t="inlineStr">
         <is>
           <t>O</t>
@@ -2163,7 +2199,7 @@
       </c>
       <c r="R22" s="0" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="S22" s="0" t="inlineStr">
@@ -2210,7 +2246,7 @@
       </c>
       <c r="H23" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I23" s="0" t="inlineStr">
@@ -2220,7 +2256,7 @@
       </c>
       <c r="J23" s="0" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K23" s="0" t="inlineStr">
@@ -2230,7 +2266,7 @@
       </c>
       <c r="L23" s="0" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M23" s="0" t="inlineStr">
@@ -2246,7 +2282,7 @@
       </c>
       <c r="P23" s="0" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Q23" s="0" t="inlineStr">
@@ -2299,7 +2335,7 @@
       </c>
       <c r="H24" s="0" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I24" s="0" t="inlineStr">
@@ -2309,7 +2345,7 @@
       </c>
       <c r="J24" s="0" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K24" s="0" t="inlineStr">
@@ -2319,7 +2355,7 @@
       </c>
       <c r="L24" s="0" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M24" s="0" t="inlineStr">
@@ -2335,7 +2371,7 @@
       </c>
       <c r="P24" s="0" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q24" s="0" t="inlineStr">
@@ -2345,12 +2381,12 @@
       </c>
       <c r="R24" s="0" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="S24" s="0" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>△</t>
         </is>
       </c>
     </row>
@@ -2420,10 +2456,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N25" s="0"/>
+      <c r="N25" s="0" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="O25" s="0" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>△</t>
         </is>
       </c>
       <c r="P25" s="0" t="inlineStr">
@@ -2438,12 +2478,12 @@
       </c>
       <c r="R25" s="0" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="S25" s="0" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>O</t>
         </is>
       </c>
     </row>
@@ -2495,7 +2535,7 @@
       </c>
       <c r="J26" s="0" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K26" s="0" t="inlineStr">
@@ -2505,7 +2545,7 @@
       </c>
       <c r="L26" s="0" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M26" s="0" t="inlineStr">
@@ -2513,15 +2553,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N26" s="0"/>
+      <c r="N26" s="0" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="O26" s="0" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>△</t>
         </is>
       </c>
       <c r="P26" s="0" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q26" s="0" t="inlineStr">
@@ -2529,10 +2573,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R26" s="0"/>
+      <c r="R26" s="0" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="S26" s="0" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>△</t>
         </is>
       </c>
     </row>
@@ -2602,14 +2650,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N27" s="0" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="N27" s="0"/>
       <c r="O27" s="0" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P27" s="0" t="inlineStr">
@@ -2624,12 +2668,12 @@
       </c>
       <c r="R27" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="S27" s="0" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>△</t>
         </is>
       </c>
     </row>
@@ -2768,7 +2812,7 @@
       </c>
       <c r="H29" s="0" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I29" s="0" t="inlineStr">
@@ -2778,22 +2822,22 @@
       </c>
       <c r="J29" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K29" s="0" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>△</t>
         </is>
       </c>
       <c r="L29" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M29" s="0" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>△</t>
         </is>
       </c>
       <c r="N29" s="0"/>
@@ -2804,7 +2848,7 @@
       </c>
       <c r="P29" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q29" s="0" t="inlineStr">
@@ -2812,10 +2856,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R29" s="0"/>
+      <c r="R29" s="0" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="S29" s="0" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>△</t>
         </is>
       </c>
     </row>
@@ -2885,14 +2933,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N30" s="0" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="N30" s="0"/>
       <c r="O30" s="0" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P30" s="0" t="inlineStr">
@@ -2905,14 +2949,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R30" s="0" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="R30" s="0"/>
       <c r="S30" s="0" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
     </row>
@@ -2952,10 +2992,14 @@
           <t>page_403_img_0_0.jpeg</t>
         </is>
       </c>
-      <c r="H31" s="0"/>
+      <c r="H31" s="0" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="I31" s="0" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J31" s="0" t="inlineStr">
@@ -2978,10 +3022,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N31" s="0"/>
+      <c r="N31" s="0" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="O31" s="0" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P31" s="0" t="inlineStr">
@@ -2996,12 +3044,12 @@
       </c>
       <c r="R31" s="0" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S31" s="0" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>O</t>
         </is>
       </c>
     </row>
@@ -3053,7 +3101,7 @@
       </c>
       <c r="J32" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K32" s="0" t="inlineStr">
@@ -3063,7 +3111,7 @@
       </c>
       <c r="L32" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M32" s="0" t="inlineStr">
@@ -3146,52 +3194,44 @@
       </c>
       <c r="J33" s="0" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K33" s="0" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L33" s="0" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M33" s="0" t="inlineStr">
         <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="N33" s="0" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N33" s="0"/>
       <c r="O33" s="0" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P33" s="0" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Q33" s="0" t="inlineStr">
         <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="R33" s="0" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="R33" s="0"/>
       <c r="S33" s="0" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>X</t>
         </is>
       </c>
     </row>
@@ -3360,7 +3400,7 @@
       </c>
       <c r="N35" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O35" s="0" t="inlineStr">
@@ -3380,7 +3420,7 @@
       </c>
       <c r="R35" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="S35" s="0" t="inlineStr">
@@ -3554,12 +3594,12 @@
       </c>
       <c r="N37" s="0" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O37" s="0" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P37" s="0" t="inlineStr">
@@ -3574,12 +3614,12 @@
       </c>
       <c r="R37" s="0" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="S37" s="0" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>O</t>
         </is>
       </c>
     </row>
@@ -3649,10 +3689,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N38" s="0"/>
+      <c r="N38" s="0" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O38" s="0" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P38" s="0" t="inlineStr">
@@ -3667,12 +3711,12 @@
       </c>
       <c r="R38" s="0" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S38" s="0" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>O</t>
         </is>
       </c>
     </row>
@@ -3938,12 +3982,12 @@
       </c>
       <c r="N41" s="0" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O41" s="0" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>△</t>
         </is>
       </c>
       <c r="P41" s="0" t="inlineStr">
@@ -3958,7 +4002,7 @@
       </c>
       <c r="R41" s="0" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="S41" s="0" t="inlineStr">
@@ -4015,7 +4059,7 @@
       </c>
       <c r="J42" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K42" s="0" t="inlineStr">
@@ -4025,7 +4069,7 @@
       </c>
       <c r="L42" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M42" s="0" t="inlineStr">
@@ -4035,7 +4079,7 @@
       </c>
       <c r="N42" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O42" s="0" t="inlineStr">
@@ -4045,7 +4089,7 @@
       </c>
       <c r="P42" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q42" s="0" t="inlineStr">
@@ -4055,7 +4099,7 @@
       </c>
       <c r="R42" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="S42" s="0" t="inlineStr">
@@ -4132,7 +4176,7 @@
       </c>
       <c r="N43" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O43" s="0" t="inlineStr">
@@ -4152,7 +4196,7 @@
       </c>
       <c r="R43" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S43" s="0" t="inlineStr">
@@ -4326,7 +4370,7 @@
       </c>
       <c r="N45" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O45" s="0" t="inlineStr">
@@ -4423,7 +4467,7 @@
       </c>
       <c r="N46" s="0" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O46" s="0" t="inlineStr">
@@ -4443,7 +4487,7 @@
       </c>
       <c r="R46" s="0" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="S46" s="0" t="inlineStr">
@@ -4500,7 +4544,7 @@
       </c>
       <c r="J47" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K47" s="0" t="inlineStr">
@@ -4510,7 +4554,7 @@
       </c>
       <c r="L47" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M47" s="0" t="inlineStr">
@@ -4520,7 +4564,7 @@
       </c>
       <c r="N47" s="0" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O47" s="0" t="inlineStr">
@@ -4530,17 +4574,17 @@
       </c>
       <c r="P47" s="0" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q47" s="0" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="R47" s="0" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="Q47" s="0" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="R47" s="0" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="S47" s="0" t="inlineStr">
@@ -4617,12 +4661,12 @@
       </c>
       <c r="N48" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O48" s="0" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>△</t>
         </is>
       </c>
       <c r="P48" s="0" t="inlineStr">
@@ -4637,7 +4681,7 @@
       </c>
       <c r="R48" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="S48" s="0" t="inlineStr">
@@ -4714,7 +4758,7 @@
       </c>
       <c r="N49" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O49" s="0" t="inlineStr">
@@ -4734,7 +4778,7 @@
       </c>
       <c r="R49" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S49" s="0" t="inlineStr">
@@ -4811,7 +4855,7 @@
       </c>
       <c r="N50" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O50" s="0" t="inlineStr">
@@ -4831,7 +4875,7 @@
       </c>
       <c r="R50" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S50" s="0" t="inlineStr">
@@ -4975,37 +5019,37 @@
       </c>
       <c r="H52" s="0" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I52" s="0" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>△</t>
         </is>
       </c>
       <c r="J52" s="0" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K52" s="0" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L52" s="0" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M52" s="0" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N52" s="0" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="K52" s="0" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L52" s="0" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M52" s="0" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="N52" s="0" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="O52" s="0" t="inlineStr">
@@ -5102,7 +5146,7 @@
       </c>
       <c r="N53" s="0" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O53" s="0" t="inlineStr">
@@ -5122,7 +5166,7 @@
       </c>
       <c r="R53" s="0" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S53" s="0" t="inlineStr">
@@ -5490,7 +5534,7 @@
       </c>
       <c r="N57" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O57" s="0" t="inlineStr">
@@ -5510,7 +5554,7 @@
       </c>
       <c r="R57" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="S57" s="0" t="inlineStr">
@@ -5751,12 +5795,12 @@
       </c>
       <c r="H60" s="0" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I60" s="0" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>△</t>
         </is>
       </c>
       <c r="J60" s="0" t="inlineStr">
@@ -5781,12 +5825,12 @@
       </c>
       <c r="N60" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O60" s="0" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>△</t>
         </is>
       </c>
       <c r="P60" s="0" t="inlineStr">
@@ -5801,7 +5845,7 @@
       </c>
       <c r="R60" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="S60" s="0" t="inlineStr">
@@ -5955,7 +5999,7 @@
       </c>
       <c r="J62" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K62" s="0" t="inlineStr">
@@ -5965,7 +6009,7 @@
       </c>
       <c r="L62" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M62" s="0" t="inlineStr">
@@ -5975,7 +6019,7 @@
       </c>
       <c r="N62" s="0" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O62" s="0" t="inlineStr">
@@ -5985,7 +6029,7 @@
       </c>
       <c r="P62" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q62" s="0" t="inlineStr">
@@ -5995,7 +6039,7 @@
       </c>
       <c r="R62" s="0" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="S62" s="0" t="inlineStr">
@@ -6072,12 +6116,12 @@
       </c>
       <c r="N63" s="0" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O63" s="0" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P63" s="0" t="inlineStr">
@@ -6139,7 +6183,7 @@
       </c>
       <c r="H64" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I64" s="0" t="inlineStr">
@@ -6266,7 +6310,7 @@
       </c>
       <c r="N65" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O65" s="0" t="inlineStr">
@@ -6286,7 +6330,7 @@
       </c>
       <c r="R65" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S65" s="0" t="inlineStr">
@@ -6343,22 +6387,22 @@
       </c>
       <c r="J66" s="0" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K66" s="0" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>△</t>
         </is>
       </c>
       <c r="L66" s="0" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M66" s="0" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>△</t>
         </is>
       </c>
       <c r="N66" s="0"/>
@@ -6369,18 +6413,22 @@
       </c>
       <c r="P66" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q66" s="0" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="R66" s="0"/>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="R66" s="0" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="S66" s="0" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
     </row>
@@ -6420,14 +6468,10 @@
           <t>page_230_img_0_0.jpeg</t>
         </is>
       </c>
-      <c r="H67" s="0" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="H67" s="0"/>
       <c r="I67" s="0" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J67" s="0" t="inlineStr">
@@ -6452,19 +6496,19 @@
       </c>
       <c r="N67" s="0" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O67" s="0" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P67" s="0" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="O67" s="0" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P67" s="0" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="Q67" s="0" t="inlineStr">
         <is>
           <t>O</t>
@@ -6472,7 +6516,7 @@
       </c>
       <c r="R67" s="0" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="S67" s="0" t="inlineStr">
@@ -6644,14 +6688,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N69" s="0" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="N69" s="0"/>
       <c r="O69" s="0" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P69" s="0" t="inlineStr">
@@ -6666,7 +6706,7 @@
       </c>
       <c r="R69" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="S69" s="0" t="inlineStr">
@@ -6743,7 +6783,7 @@
       </c>
       <c r="N70" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O70" s="0" t="inlineStr">
@@ -6763,7 +6803,7 @@
       </c>
       <c r="R70" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="S70" s="0" t="inlineStr">
@@ -6840,7 +6880,7 @@
       </c>
       <c r="N71" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O71" s="0" t="inlineStr">
@@ -6860,7 +6900,7 @@
       </c>
       <c r="R71" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="S71" s="0" t="inlineStr">

--- a/SCIE용/산출물/엑셀/15_g1_g2_g3_g4_retrieval_results.xlsx
+++ b/SCIE용/산출물/엑셀/15_g1_g2_g3_g4_retrieval_results.xlsx
@@ -225,7 +225,7 @@
       </c>
       <c r="H2" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I2" s="0" t="inlineStr">
@@ -253,14 +253,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N2" s="0" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="N2" s="0"/>
       <c r="O2" s="0" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P2" s="0" t="inlineStr">
@@ -273,14 +269,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R2" s="0" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="R2" s="0"/>
       <c r="S2" s="0" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
     </row>
@@ -352,7 +344,7 @@
       </c>
       <c r="N3" s="0" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O3" s="0" t="inlineStr">
@@ -449,7 +441,7 @@
       </c>
       <c r="N4" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O4" s="0" t="inlineStr">
@@ -566,7 +558,7 @@
       </c>
       <c r="R5" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S5" s="0" t="inlineStr">
@@ -730,14 +722,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N7" s="0" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="N7" s="0"/>
       <c r="O7" s="0" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P7" s="0" t="inlineStr">
@@ -829,27 +817,27 @@
       </c>
       <c r="N8" s="0" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="O8" s="0" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="P8" s="0" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q8" s="0" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="R8" s="0" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="O8" s="0" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P8" s="0" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Q8" s="0" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="R8" s="0" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="S8" s="0" t="inlineStr">
@@ -926,7 +914,7 @@
       </c>
       <c r="N9" s="0" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O9" s="0" t="inlineStr">
@@ -946,7 +934,7 @@
       </c>
       <c r="R9" s="0" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S9" s="0" t="inlineStr">
@@ -1023,7 +1011,7 @@
       </c>
       <c r="N10" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O10" s="0" t="inlineStr">
@@ -1043,7 +1031,7 @@
       </c>
       <c r="R10" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="S10" s="0" t="inlineStr">
@@ -1090,7 +1078,7 @@
       </c>
       <c r="H11" s="0" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I11" s="0" t="inlineStr">
@@ -1100,7 +1088,7 @@
       </c>
       <c r="J11" s="0" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K11" s="0" t="inlineStr">
@@ -1110,7 +1098,7 @@
       </c>
       <c r="L11" s="0" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M11" s="0" t="inlineStr">
@@ -1126,7 +1114,7 @@
       </c>
       <c r="P11" s="0" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Q11" s="0" t="inlineStr">
@@ -1207,14 +1195,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N12" s="0" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="N12" s="0"/>
       <c r="O12" s="0" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P12" s="0" t="inlineStr">
@@ -1227,14 +1211,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R12" s="0" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="R12" s="0"/>
       <c r="S12" s="0" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1403,7 @@
       </c>
       <c r="R14" s="0" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S14" s="0" t="inlineStr">
@@ -1595,14 +1575,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N16" s="0" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="N16" s="0"/>
       <c r="O16" s="0" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P16" s="0" t="inlineStr">
@@ -1615,14 +1591,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R16" s="0" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="R16" s="0"/>
       <c r="S16" s="0" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
     </row>
@@ -1664,12 +1636,12 @@
       </c>
       <c r="H17" s="0" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I17" s="0" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J17" s="0" t="inlineStr">
@@ -1983,34 +1955,30 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N20" s="0" t="inlineStr">
+      <c r="N20" s="0"/>
+      <c r="O20" s="0" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P20" s="0" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q20" s="0" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="R20" s="0" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="O20" s="0" t="inlineStr">
+      <c r="S20" s="0" t="inlineStr">
         <is>
           <t>△</t>
-        </is>
-      </c>
-      <c r="P20" s="0" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Q20" s="0" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="R20" s="0" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="S20" s="0" t="inlineStr">
-        <is>
-          <t>O</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2020,7 @@
       </c>
       <c r="H21" s="0" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I21" s="0" t="inlineStr">
@@ -2082,7 +2050,7 @@
       </c>
       <c r="N21" s="0" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O21" s="0" t="inlineStr">
@@ -2159,47 +2127,47 @@
       </c>
       <c r="J22" s="0" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" s="0" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L22" s="0" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M22" s="0" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N22" s="0" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="K22" s="0" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L22" s="0" t="inlineStr">
+      <c r="O22" s="0" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P22" s="0" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q22" s="0" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="R22" s="0" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="M22" s="0" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="N22" s="0" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="O22" s="0" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P22" s="0" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Q22" s="0" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="R22" s="0" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="S22" s="0" t="inlineStr">
@@ -2246,7 +2214,7 @@
       </c>
       <c r="H23" s="0" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I23" s="0" t="inlineStr">
@@ -2256,7 +2224,7 @@
       </c>
       <c r="J23" s="0" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K23" s="0" t="inlineStr">
@@ -2266,7 +2234,7 @@
       </c>
       <c r="L23" s="0" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M23" s="0" t="inlineStr">
@@ -2282,7 +2250,7 @@
       </c>
       <c r="P23" s="0" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q23" s="0" t="inlineStr">
@@ -2335,19 +2303,19 @@
       </c>
       <c r="H24" s="0" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I24" s="0" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J24" s="0" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I24" s="0" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J24" s="0" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K24" s="0" t="inlineStr">
         <is>
           <t>O</t>
@@ -2355,7 +2323,7 @@
       </c>
       <c r="L24" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M24" s="0" t="inlineStr">
@@ -2371,7 +2339,7 @@
       </c>
       <c r="P24" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Q24" s="0" t="inlineStr">
@@ -2381,12 +2349,12 @@
       </c>
       <c r="R24" s="0" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="S24" s="0" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>O</t>
         </is>
       </c>
     </row>
@@ -2458,12 +2426,12 @@
       </c>
       <c r="N25" s="0" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O25" s="0" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P25" s="0" t="inlineStr">
@@ -2478,7 +2446,7 @@
       </c>
       <c r="R25" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S25" s="0" t="inlineStr">
@@ -2535,7 +2503,7 @@
       </c>
       <c r="J26" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K26" s="0" t="inlineStr">
@@ -2545,7 +2513,7 @@
       </c>
       <c r="L26" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M26" s="0" t="inlineStr">
@@ -2565,7 +2533,7 @@
       </c>
       <c r="P26" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q26" s="0" t="inlineStr">
@@ -2650,10 +2618,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N27" s="0"/>
+      <c r="N27" s="0" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O27" s="0" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P27" s="0" t="inlineStr">
@@ -2668,12 +2640,12 @@
       </c>
       <c r="R27" s="0" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="S27" s="0" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>O</t>
         </is>
       </c>
     </row>
@@ -2812,7 +2784,7 @@
       </c>
       <c r="H29" s="0" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I29" s="0" t="inlineStr">
@@ -2822,22 +2794,22 @@
       </c>
       <c r="J29" s="0" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K29" s="0" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L29" s="0" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M29" s="0" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>O</t>
         </is>
       </c>
       <c r="N29" s="0"/>
@@ -2848,7 +2820,7 @@
       </c>
       <c r="P29" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q29" s="0" t="inlineStr">
@@ -2856,14 +2828,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R29" s="0" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="R29" s="0"/>
       <c r="S29" s="0" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>X</t>
         </is>
       </c>
     </row>
@@ -2992,14 +2960,10 @@
           <t>page_403_img_0_0.jpeg</t>
         </is>
       </c>
-      <c r="H31" s="0" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="H31" s="0"/>
       <c r="I31" s="0" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J31" s="0" t="inlineStr">
@@ -3022,14 +2986,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N31" s="0" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="N31" s="0"/>
       <c r="O31" s="0" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P31" s="0" t="inlineStr">
@@ -3044,7 +3004,7 @@
       </c>
       <c r="R31" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="S31" s="0" t="inlineStr">
@@ -3101,7 +3061,7 @@
       </c>
       <c r="J32" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K32" s="0" t="inlineStr">
@@ -3111,7 +3071,7 @@
       </c>
       <c r="L32" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M32" s="0" t="inlineStr">
@@ -3119,10 +3079,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N32" s="0"/>
+      <c r="N32" s="0" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="O32" s="0" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>△</t>
         </is>
       </c>
       <c r="P32" s="0" t="inlineStr">
@@ -3194,44 +3158,52 @@
       </c>
       <c r="J33" s="0" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K33" s="0" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>△</t>
         </is>
       </c>
       <c r="L33" s="0" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M33" s="0" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="N33" s="0"/>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="N33" s="0" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="O33" s="0" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>△</t>
         </is>
       </c>
       <c r="P33" s="0" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Q33" s="0" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="R33" s="0"/>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="R33" s="0" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="S33" s="0" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>△</t>
         </is>
       </c>
     </row>
@@ -3400,7 +3372,7 @@
       </c>
       <c r="N35" s="0" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O35" s="0" t="inlineStr">
@@ -3420,7 +3392,7 @@
       </c>
       <c r="R35" s="0" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="S35" s="0" t="inlineStr">
@@ -3594,7 +3566,7 @@
       </c>
       <c r="N37" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O37" s="0" t="inlineStr">
@@ -3614,7 +3586,7 @@
       </c>
       <c r="R37" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S37" s="0" t="inlineStr">
@@ -3689,14 +3661,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N38" s="0" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="N38" s="0"/>
       <c r="O38" s="0" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P38" s="0" t="inlineStr">
@@ -3711,12 +3679,12 @@
       </c>
       <c r="R38" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="S38" s="0" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>△</t>
         </is>
       </c>
     </row>
@@ -3788,7 +3756,7 @@
       </c>
       <c r="N39" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O39" s="0" t="inlineStr">
@@ -3808,7 +3776,7 @@
       </c>
       <c r="R39" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S39" s="0" t="inlineStr">
@@ -3982,7 +3950,7 @@
       </c>
       <c r="N41" s="0" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O41" s="0" t="inlineStr">
@@ -4002,12 +3970,12 @@
       </c>
       <c r="R41" s="0" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="S41" s="0" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>△</t>
         </is>
       </c>
     </row>
@@ -4059,7 +4027,7 @@
       </c>
       <c r="J42" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K42" s="0" t="inlineStr">
@@ -4069,7 +4037,7 @@
       </c>
       <c r="L42" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M42" s="0" t="inlineStr">
@@ -4079,7 +4047,7 @@
       </c>
       <c r="N42" s="0" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O42" s="0" t="inlineStr">
@@ -4089,7 +4057,7 @@
       </c>
       <c r="P42" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q42" s="0" t="inlineStr">
@@ -4099,7 +4067,7 @@
       </c>
       <c r="R42" s="0" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="S42" s="0" t="inlineStr">
@@ -4176,7 +4144,7 @@
       </c>
       <c r="N43" s="0" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O43" s="0" t="inlineStr">
@@ -4196,7 +4164,7 @@
       </c>
       <c r="R43" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="S43" s="0" t="inlineStr">
@@ -4544,39 +4512,39 @@
       </c>
       <c r="J47" s="0" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K47" s="0" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L47" s="0" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M47" s="0" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N47" s="0" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O47" s="0" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P47" s="0" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K47" s="0" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L47" s="0" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M47" s="0" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="N47" s="0" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="O47" s="0" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P47" s="0" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="Q47" s="0" t="inlineStr">
         <is>
           <t>O</t>
@@ -4584,7 +4552,7 @@
       </c>
       <c r="R47" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="S47" s="0" t="inlineStr">
@@ -4661,12 +4629,12 @@
       </c>
       <c r="N48" s="0" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O48" s="0" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P48" s="0" t="inlineStr">
@@ -4681,7 +4649,7 @@
       </c>
       <c r="R48" s="0" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S48" s="0" t="inlineStr">
@@ -4778,7 +4746,7 @@
       </c>
       <c r="R49" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="S49" s="0" t="inlineStr">
@@ -5019,17 +4987,17 @@
       </c>
       <c r="H52" s="0" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I52" s="0" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J52" s="0" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K52" s="0" t="inlineStr">
@@ -5039,7 +5007,7 @@
       </c>
       <c r="L52" s="0" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M52" s="0" t="inlineStr">
@@ -5049,7 +5017,7 @@
       </c>
       <c r="N52" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O52" s="0" t="inlineStr">
@@ -5534,7 +5502,7 @@
       </c>
       <c r="N57" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O57" s="0" t="inlineStr">
@@ -5554,7 +5522,7 @@
       </c>
       <c r="R57" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S57" s="0" t="inlineStr">
@@ -5795,12 +5763,12 @@
       </c>
       <c r="H60" s="0" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I60" s="0" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J60" s="0" t="inlineStr">
@@ -5825,12 +5793,12 @@
       </c>
       <c r="N60" s="0" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O60" s="0" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P60" s="0" t="inlineStr">
@@ -5845,7 +5813,7 @@
       </c>
       <c r="R60" s="0" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S60" s="0" t="inlineStr">
@@ -5999,47 +5967,47 @@
       </c>
       <c r="J62" s="0" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K62" s="0" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L62" s="0" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M62" s="0" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="N62" s="0" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K62" s="0" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L62" s="0" t="inlineStr">
+      <c r="O62" s="0" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P62" s="0" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q62" s="0" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="R62" s="0" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="M62" s="0" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="N62" s="0" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="O62" s="0" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P62" s="0" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q62" s="0" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="R62" s="0" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="S62" s="0" t="inlineStr">
@@ -6183,7 +6151,7 @@
       </c>
       <c r="H64" s="0" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I64" s="0" t="inlineStr">
@@ -6387,22 +6355,22 @@
       </c>
       <c r="J66" s="0" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K66" s="0" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L66" s="0" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M66" s="0" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>O</t>
         </is>
       </c>
       <c r="N66" s="0"/>
@@ -6413,22 +6381,18 @@
       </c>
       <c r="P66" s="0" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q66" s="0" t="inlineStr">
         <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="R66" s="0" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="R66" s="0"/>
       <c r="S66" s="0" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
     </row>
@@ -6468,10 +6432,14 @@
           <t>page_230_img_0_0.jpeg</t>
         </is>
       </c>
-      <c r="H67" s="0"/>
+      <c r="H67" s="0" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="I67" s="0" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>△</t>
         </is>
       </c>
       <c r="J67" s="0" t="inlineStr">
@@ -6496,12 +6464,12 @@
       </c>
       <c r="N67" s="0" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O67" s="0" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>△</t>
         </is>
       </c>
       <c r="P67" s="0" t="inlineStr">
@@ -6516,12 +6484,12 @@
       </c>
       <c r="R67" s="0" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="S67" s="0" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>△</t>
         </is>
       </c>
     </row>
@@ -6688,10 +6656,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N69" s="0"/>
+      <c r="N69" s="0" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="O69" s="0" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P69" s="0" t="inlineStr">
@@ -6706,7 +6678,7 @@
       </c>
       <c r="R69" s="0" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S69" s="0" t="inlineStr">
@@ -6783,7 +6755,7 @@
       </c>
       <c r="N70" s="0" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O70" s="0" t="inlineStr">
@@ -6803,7 +6775,7 @@
       </c>
       <c r="R70" s="0" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S70" s="0" t="inlineStr">
@@ -6880,7 +6852,7 @@
       </c>
       <c r="N71" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O71" s="0" t="inlineStr">
@@ -6900,7 +6872,7 @@
       </c>
       <c r="R71" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S71" s="0" t="inlineStr">
